--- a/workbooks/10 Formulas 6 - Dates.xlsx
+++ b/workbooks/10 Formulas 6 - Dates.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="635">
   <si>
     <t>Challenge</t>
   </si>
@@ -2036,22 +2036,70 @@
     <t>Boss F5</t>
   </si>
   <si>
+    <t>After lookup, lookup array, return array.</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>FOURTH</t>
+  </si>
+  <si>
+    <t>IF_NOT_FOUND</t>
+  </si>
+  <si>
     <t>F5</t>
   </si>
   <si>
     <t>Boss F6</t>
   </si>
   <si>
+    <t>Count E and F.</t>
+  </si>
+  <si>
+    <t>TWO</t>
+  </si>
+  <si>
     <t>F6</t>
   </si>
   <si>
     <t>Boss F7</t>
   </si>
   <si>
+    <t>V for vertical.</t>
+  </si>
+  <si>
+    <t>=VLOOKUP</t>
+  </si>
+  <si>
+    <t>=VLOOKUP(</t>
+  </si>
+  <si>
+    <t>=VLOOKUP()</t>
+  </si>
+  <si>
+    <t>VLOOKUP</t>
+  </si>
+  <si>
+    <t>VLOOKUP(</t>
+  </si>
+  <si>
+    <t>VLOOKUP()</t>
+  </si>
+  <si>
     <t>F7</t>
   </si>
   <si>
     <t>Boss F8</t>
+  </si>
+  <si>
+    <t>The opposite of TRUE.</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>FALSE</t>
   </si>
   <si>
     <t>F8</t>
@@ -3051,7 +3099,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3061,12 +3109,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3076,32 +3124,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3111,30 +3159,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F6-1 Calendar'!$G$17:$G$53)&amp;" / 300"</f>
@@ -3149,15 +3197,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F6-2 Date Math'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3172,15 +3220,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F6-3 Deadlines'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3195,15 +3243,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3218,12 +3266,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="B18" s="12" cm="1" t="str">
         <f t="array" ref="B18">(SUM('F6-1 Calendar'!$G$17:$G$53)+SUM('F6-2 Date Math'!$G$13:$G$39)+SUM('F6-3 Deadlines'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 880"</f>
@@ -3232,19 +3280,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('F6-1 Calendar'!$G$17:$G$53)+SUM('F6-2 Date Math'!$G$13:$G$39)+SUM('F6-3 Deadlines'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/880,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=12),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 12)","—")</f>
@@ -3253,7 +3301,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3262,7 +3310,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -3295,7 +3343,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3303,217 +3351,217 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>268</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>157</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>359</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>156</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -5216,195 +5264,165 @@
         <v>510</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>511</v>
       </c>
       <c r="E78" t="s">
-        <v>173</v>
+        <v>30</v>
       </c>
       <c r="F78" t="s">
-        <v>174</v>
+        <v>512</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
+        <v>513</v>
       </c>
       <c r="H78" t="s">
-        <v>23</v>
-      </c>
-      <c r="I78" t="s">
-        <v>176</v>
-      </c>
-      <c r="J78" t="s">
-        <v>177</v>
+        <v>514</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s">
-        <v>147</v>
+        <v>517</v>
       </c>
       <c r="E79" t="s">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="F79" t="s">
-        <v>181</v>
-      </c>
-      <c r="G79" t="s">
-        <v>182</v>
-      </c>
-      <c r="H79" t="s">
-        <v>26</v>
-      </c>
-      <c r="I79" t="s">
-        <v>183</v>
-      </c>
-      <c r="J79" t="s">
-        <v>184</v>
+        <v>518</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s">
-        <v>152</v>
+        <v>521</v>
       </c>
       <c r="E80" t="s">
-        <v>187</v>
+        <v>522</v>
       </c>
       <c r="F80" t="s">
-        <v>188</v>
+        <v>523</v>
       </c>
       <c r="G80" t="s">
-        <v>189</v>
+        <v>524</v>
       </c>
       <c r="H80" t="s">
-        <v>29</v>
+        <v>525</v>
       </c>
       <c r="I80" t="s">
-        <v>190</v>
+        <v>526</v>
       </c>
       <c r="J80" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>530</v>
       </c>
       <c r="E81" t="s">
-        <v>194</v>
+        <v>531</v>
       </c>
       <c r="F81" t="s">
-        <v>195</v>
-      </c>
-      <c r="G81" t="s">
-        <v>196</v>
-      </c>
-      <c r="H81" t="s">
-        <v>32</v>
-      </c>
-      <c r="I81" t="s">
-        <v>197</v>
-      </c>
-      <c r="J81" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B82" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="C82" cm="1">
         <f t="array" ref="C82">YEAR('Boss Arena'!$B$6)</f>
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="C83" cm="1">
         <f t="array" ref="C83">WEEKDAY('Boss Arena'!$B$6)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="C84" cm="1">
         <f t="array" ref="C84">'Boss Arena'!$B$7-'Boss Arena'!$B$6</f>
         <v>79</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="C85" cm="1">
         <f t="array" ref="C85">DATEDIF('Boss Arena'!$B$8,'Boss Arena'!$B$6,"Y")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="B86" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="C86" cm="1">
         <f t="array" ref="C86">EDATE('Boss Arena'!$B$6,2)</f>
         <v>46335</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="C87" cm="1">
         <f t="array" ref="C87">EOMONTH('Boss Arena'!$B$7,0)</f>
         <v>46356</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="C88" cm="1">
         <f t="array" ref="C88">NETWORKDAYS('Boss Arena'!$B$6,'Boss Arena'!$B$7)</f>
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="C89" cm="1">
         <f t="array" ref="C89">WORKDAY('Boss Arena'!$B$6,15)</f>
@@ -8411,7 +8429,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8422,7 +8440,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8620,15 +8638,15 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B18" s="33" cm="1" t="str">
-        <f t="array" ref="B18">IF($C$10="OPEN","Which function returns today's date?  (from F6-1 Calendar)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B18">IF($C$10="OPEN","Which XLOOKUP argument number sets the result when no match is found?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
-        <f t="array" ref="D18">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$18,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$78:$J$78),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D18">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$18,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$78:$H$78),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E18" s="22"/>
@@ -8641,17 +8659,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="35.5" customHeight="1">
+    <row r="19" spans="1:7" ht="51.25" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B19" s="33" cm="1" t="str">
-        <f t="array" ref="B19">IF($C$10="OPEN","Which function returns the current date and time?  (from F6-1 Calendar)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B19">IF($C$10="OPEN","If the return array is E6:F20, how many columns does the result spill into?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
-        <f t="array" ref="D19">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$19,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$79:$J$79),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D19">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$19,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$79:$F$79),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E19" s="22"/>
@@ -8664,12 +8682,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="35.5" customHeight="1">
+    <row r="20" spans="1:7" ht="51.25" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="B20" s="33" cm="1" t="str">
-        <f t="array" ref="B20">IF($C$10="OPEN","Which function builds a date from a year, month and day?  (from F6-1 Calendar)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B20">IF($C$10="OPEN","Which classic function searches the first column of a table and returns a column by number?  (from F4-3 Old School)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C20" s="20"/>
@@ -8689,15 +8707,15 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="B21" s="33" cm="1" t="str">
-        <f t="array" ref="B21">IF($C$10="OPEN","Which function returns the year of a date?  (from F6-1 Calendar)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B21">IF($C$10="OPEN","Which 4th argument makes VLOOKUP find an exact match?  (from F4-3 Old School)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
-        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$J$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$F$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E21" s="22"/>
@@ -8712,7 +8730,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8723,7 +8741,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8751,14 +8769,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="B26" s="33" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In D6 return the year of B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$6),ABS('Boss Arena'!$D$6-Key!$C$82)&lt;=1E-9*MAX(1,ABS(Key!$C$82))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"YEAR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use YEAR"))))),"LOCKED")</f>
@@ -8776,14 +8794,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B27" s="33" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In D7 return the weekday number of B6 (Sunday = 1).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$7),ABS('Boss Arena'!$D$7-Key!$C$83)&lt;=1E-9*MAX(1,ABS(Key!$C$83))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"WEEKDAY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use WEEKDAY"))))),"LOCKED")</f>
@@ -8801,14 +8819,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B28" s="33" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In D8 count the days from B6 to B7.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$8),ABS('Boss Arena'!$D$8-Key!$C$84)&lt;=1E-9*MAX(1,ABS(Key!$C$84))),FALSE))),"✘ TRY AGAIN","✔ CLEAR")))),"LOCKED")</f>
@@ -8826,14 +8844,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="B29" s="33" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In D9 count the full years from B8 to B6 with DATEDIF.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$9),ABS('Boss Arena'!$D$9-Key!$C$85)&lt;=1E-9*MAX(1,ABS(Key!$C$85))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"DATEDIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use DATEDIF"))))),"LOCKED")</f>
@@ -8851,14 +8869,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="B30" s="33" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In D10 return the date 2 months after B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$10),ABS('Boss Arena'!$D$10-Key!$C$86)&lt;=1E-9*MAX(1,ABS(Key!$C$86))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EDATE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use EDATE"))))),"LOCKED")</f>
@@ -8876,14 +8894,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="B31" s="33" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In D11 return the last day of B7's month.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$11),ABS('Boss Arena'!$D$11-Key!$C$87)&lt;=1E-9*MAX(1,ABS(Key!$C$87))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EOMONTH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use EOMONTH"))))),"LOCKED")</f>
@@ -8901,14 +8919,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="B32" s="33" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In D12 count the working days from B6 to B7.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$12),ABS('Boss Arena'!$D$12-Key!$C$88)&lt;=1E-9*MAX(1,ABS(Key!$C$88))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NETWORKDAYS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use NETWORKDAYS"))))),"LOCKED")</f>
@@ -8926,14 +8944,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B33" s="33" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In D13 return the date 15 working days after B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$13),ABS('Boss Arena'!$D$13-Key!$C$89)&lt;=1E-9*MAX(1,ABS(Key!$C$89))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"WORKDAY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$13)))))),"✔ CLEAR","✘ CLOSE · right value, but use WORKDAY"))))),"LOCKED")</f>

--- a/workbooks/10 Formulas 6 - Dates.xlsx
+++ b/workbooks/10 Formulas 6 - Dates.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="637">
   <si>
     <t>Challenge</t>
   </si>
@@ -1302,55 +1302,61 @@
     <t>=B2*C2</t>
   </si>
   <si>
+    <t>Which move is this? Subtract two dates to get the days between them.</t>
+  </si>
+  <si>
+    <t>F6-2 Date Math T2</t>
+  </si>
+  <si>
+    <t>Plain plus.</t>
+  </si>
+  <si>
+    <t>* and ?</t>
+  </si>
+  <si>
+    <t>Which move is this? Add a number to a date to move forward that many days.</t>
+  </si>
+  <si>
+    <t>F6-2 Date Math T3</t>
+  </si>
+  <si>
+    <t>DATE plus DIF.</t>
+  </si>
+  <si>
+    <t>Which function counts full years or months between two dates?</t>
+  </si>
+  <si>
+    <t>▶ Open F6-2 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F6-2 Date Math C1</t>
+  </si>
+  <si>
+    <t>DAYS</t>
+  </si>
+  <si>
+    <t>NUMBEROFDAYS</t>
+  </si>
+  <si>
     <t>What do you get when you subtract an earlier date from a later one (one word)?</t>
   </si>
   <si>
-    <t>F6-2 Date Math T2</t>
-  </si>
-  <si>
-    <t>Plain plus.</t>
-  </si>
-  <si>
-    <t>* and ?</t>
+    <t>F6-2 Date Math C2</t>
+  </si>
+  <si>
+    <t>30+B6</t>
+  </si>
+  <si>
+    <t>=30+B6</t>
+  </si>
+  <si>
+    <t>=B6+30</t>
+  </si>
+  <si>
+    <t>B6+30</t>
   </si>
   <si>
     <t>Type the formula for the date 30 days after the date in B6.</t>
-  </si>
-  <si>
-    <t>F6-2 Date Math T3</t>
-  </si>
-  <si>
-    <t>DATE plus DIF.</t>
-  </si>
-  <si>
-    <t>Which function counts full years or months between two dates?</t>
-  </si>
-  <si>
-    <t>▶ Open F6-2 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F6-2 Date Math C1</t>
-  </si>
-  <si>
-    <t>DAYS</t>
-  </si>
-  <si>
-    <t>NUMBEROFDAYS</t>
-  </si>
-  <si>
-    <t>F6-2 Date Math C2</t>
-  </si>
-  <si>
-    <t>30+B6</t>
-  </si>
-  <si>
-    <t>=30+B6</t>
-  </si>
-  <si>
-    <t>=B6+30</t>
-  </si>
-  <si>
-    <t>B6+30</t>
   </si>
   <si>
     <t>F6-2 Date Math C3</t>
@@ -3099,7 +3105,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3109,12 +3115,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3124,32 +3130,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3159,30 +3165,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F6-1 Calendar'!$G$17:$G$53)&amp;" / 300"</f>
@@ -3197,15 +3203,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F6-2 Date Math'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3220,15 +3226,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F6-3 Deadlines'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3243,15 +3249,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3266,12 +3272,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B18" s="12" cm="1" t="str">
         <f t="array" ref="B18">(SUM('F6-1 Calendar'!$G$17:$G$53)+SUM('F6-2 Date Math'!$G$13:$G$39)+SUM('F6-3 Deadlines'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 880"</f>
@@ -3280,19 +3286,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('F6-1 Calendar'!$G$17:$G$53)+SUM('F6-2 Date Math'!$G$13:$G$39)+SUM('F6-3 Deadlines'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/880,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=12),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 12)","—")</f>
@@ -3301,7 +3307,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3310,7 +3316,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -3343,7 +3349,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3351,217 +3357,217 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>268</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>157</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>156</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -4571,56 +4577,56 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s">
         <v>311</v>
       </c>
       <c r="E46" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F46" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G46" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s">
         <v>315</v>
       </c>
       <c r="E47" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G47" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H47" t="s">
         <v>148</v>
       </c>
       <c r="I47" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J47" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C48" cm="1">
         <f t="array" ref="C48">'F6-2 Arena'!$B$7-'F6-2 Arena'!$B$6</f>
@@ -4629,10 +4635,10 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C49" cm="1">
         <f t="array" ref="C49">'F6-2 Arena'!$B$6+30</f>
@@ -4641,10 +4647,10 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C50" cm="1">
         <f t="array" ref="C50">DATEDIF('F6-2 Arena'!$B$9,'F6-2 Arena'!$B$10,"Y")</f>
@@ -4653,10 +4659,10 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B51" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C51" cm="1">
         <f t="array" ref="C51">DATEDIF('F6-2 Arena'!$B$6,'F6-2 Arena'!$B$7,"M")</f>
@@ -4665,7 +4671,7 @@
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s">
         <v>306</v>
@@ -4679,244 +4685,244 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B53" t="s">
         <v>311</v>
       </c>
       <c r="E53" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F53" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G53" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H53" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B54" t="s">
         <v>315</v>
       </c>
       <c r="E54" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F54" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G54" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H54" t="s">
         <v>148</v>
       </c>
       <c r="I54" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J54" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B55" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E55" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F55" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G55" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H55" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I55" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J55" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s">
         <v>152</v>
       </c>
       <c r="E56" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F56" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G56" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H56" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I56" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J56" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E57" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F57" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G57" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H57" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I57" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J57" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B58" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E58" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F58" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G58" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H58" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I58" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J58" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K58" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L58" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M58" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N58" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O58" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P58" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q58" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="R58" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="S58" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="T58" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E60" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F60" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G60" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H60" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I60" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J60" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B61" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E61" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F61" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G61" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B62" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C62" t="s">
         <v>157</v>
@@ -4936,10 +4942,10 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B63" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C63" t="s">
         <v>143</v>
@@ -4959,13 +4965,13 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B64" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C64" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E64" t="s">
         <v>156</v>
@@ -4974,7 +4980,7 @@
         <v>148</v>
       </c>
       <c r="G64" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H64" t="s">
         <v>29</v>
@@ -4982,10 +4988,10 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B65" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C65" t="s">
         <v>156</v>
@@ -5005,114 +5011,114 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B66" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E66" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F66" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G66" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H66" t="s">
         <v>157</v>
       </c>
       <c r="I66" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J66" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E67" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F67" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G67" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H67" t="s">
         <v>143</v>
       </c>
       <c r="I67" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J67" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B68" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E68" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F68" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G68" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H68" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I68" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J68" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B69" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E69" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F69" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G69" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H69" t="s">
         <v>156</v>
       </c>
       <c r="I69" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J69" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C70" cm="1">
         <f t="array" ref="C70">EDATE('F6-3 Arena'!$B$6,3)</f>
@@ -5121,10 +5127,10 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C71" cm="1">
         <f t="array" ref="C71">EOMONTH('F6-3 Arena'!$B$6,0)</f>
@@ -5133,10 +5139,10 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C72" cm="1">
         <f t="array" ref="C72">NETWORKDAYS('F6-3 Arena'!$B$6,'F6-3 Arena'!$B$7)</f>
@@ -5145,10 +5151,10 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C73" cm="1">
         <f t="array" ref="C73">WORKDAY('F6-3 Arena'!$B$6,10)</f>
@@ -5157,188 +5163,188 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E74" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F74" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G74" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H74" t="s">
         <v>157</v>
       </c>
       <c r="I74" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J74" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B75" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E75" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F75" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G75" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H75" t="s">
         <v>143</v>
       </c>
       <c r="I75" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J75" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B76" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E76" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F76" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G76" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H76" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I76" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J76" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B77" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E77" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F77" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G77" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H77" t="s">
         <v>156</v>
       </c>
       <c r="I77" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J77" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E78" t="s">
         <v>30</v>
       </c>
       <c r="F78" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G78" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H78" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E79" t="s">
         <v>24</v>
       </c>
       <c r="F79" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B80" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E80" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F80" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G80" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="H80" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I80" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J80" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B81" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E81" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F81" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B82" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C82" cm="1">
         <f t="array" ref="C82">YEAR('Boss Arena'!$B$6)</f>
@@ -5347,10 +5353,10 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C83" cm="1">
         <f t="array" ref="C83">WEEKDAY('Boss Arena'!$B$6)</f>
@@ -5359,10 +5365,10 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B84" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C84" cm="1">
         <f t="array" ref="C84">'Boss Arena'!$B$7-'Boss Arena'!$B$6</f>
@@ -5371,10 +5377,10 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B85" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C85" cm="1">
         <f t="array" ref="C85">DATEDIF('Boss Arena'!$B$8,'Boss Arena'!$B$6,"Y")</f>
@@ -5383,10 +5389,10 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B86" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C86" cm="1">
         <f t="array" ref="C86">EDATE('Boss Arena'!$B$6,2)</f>
@@ -5395,10 +5401,10 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C87" cm="1">
         <f t="array" ref="C87">EOMONTH('Boss Arena'!$B$7,0)</f>
@@ -5407,10 +5413,10 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C88" cm="1">
         <f t="array" ref="C88">NETWORKDAYS('Boss Arena'!$B$6,'Boss Arena'!$B$7)</f>
@@ -5419,10 +5425,10 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C89" cm="1">
         <f t="array" ref="C89">WORKDAY('Boss Arena'!$B$6,15)</f>
@@ -6632,7 +6638,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6643,7 +6649,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7121,7 +7127,7 @@
         <v>178</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -7143,7 +7149,7 @@
         <v>185</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -7187,10 +7193,10 @@
         <v>199</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F6-2 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F6-2 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-2 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-2 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-2 Arena'!$D$6),ABS('F6-2 Arena'!$D$6-Key!$C$48)&lt;=1E-9*MAX(1,ABS(Key!$C$48))),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -7211,10 +7217,10 @@
         <v>206</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F6-2 Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('F6-2 Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-2 Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-2 Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-2 Arena'!$D$7),ABS('F6-2 Arena'!$D$7-Key!$C$49)&lt;=1E-9*MAX(1,ABS(Key!$C$49))),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -7235,10 +7241,10 @@
         <v>213</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F6-2 Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('F6-2 Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-2 Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-2 Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-2 Arena'!$D$8),ABS('F6-2 Arena'!$D$8-Key!$C$50)&lt;=1E-9*MAX(1,ABS(Key!$C$50))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"DATEDIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F6-2 Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use DATEDIF")))))</f>
@@ -7259,10 +7265,10 @@
         <v>220</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F6-2 Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('F6-2 Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-2 Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-2 Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-2 Arena'!$D$9),ABS('F6-2 Arena'!$D$9-Key!$C$51)&lt;=1E-9*MAX(1,ABS(Key!$C$51))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"DATEDIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F6-2 Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use DATEDIF")))))</f>
@@ -7505,7 +7511,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7516,7 +7522,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7568,7 +7574,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>157</v>
@@ -7579,7 +7585,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>143</v>
@@ -7590,10 +7596,10 @@
         <v>27</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="51.25" customHeight="1">
@@ -7601,7 +7607,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>156</v>
@@ -7646,7 +7652,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -7668,7 +7674,7 @@
         <v>66</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -7690,7 +7696,7 @@
         <v>76</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -7712,7 +7718,7 @@
         <v>86</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -7734,7 +7740,7 @@
         <v>96</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -7756,7 +7762,7 @@
         <v>101</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -7778,7 +7784,7 @@
         <v>107</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -7800,7 +7806,7 @@
         <v>112</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -7822,7 +7828,7 @@
         <v>118</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -7844,7 +7850,7 @@
         <v>138</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -7900,7 +7906,7 @@
         <v>144</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -7922,7 +7928,7 @@
         <v>149</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -7944,7 +7950,7 @@
         <v>153</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -7966,7 +7972,7 @@
         <v>158</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -7996,7 +8002,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -8027,7 +8033,7 @@
         <v>178</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -8049,7 +8055,7 @@
         <v>185</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -8071,7 +8077,7 @@
         <v>192</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -8093,7 +8099,7 @@
         <v>199</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -8115,10 +8121,10 @@
         <v>206</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F6-3 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F6-3 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-3 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-3 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-3 Arena'!$D$6),ABS('F6-3 Arena'!$D$6-Key!$C$70)&lt;=1E-9*MAX(1,ABS(Key!$C$70))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EDATE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F6-3 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use EDATE")))))</f>
@@ -8139,10 +8145,10 @@
         <v>213</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(ISBLANK('F6-3 Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('F6-3 Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-3 Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-3 Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-3 Arena'!$D$7),ABS('F6-3 Arena'!$D$7-Key!$C$71)&lt;=1E-9*MAX(1,ABS(Key!$C$71))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EOMONTH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F6-3 Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use EOMONTH")))))</f>
@@ -8163,10 +8169,10 @@
         <v>220</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(ISBLANK('F6-3 Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('F6-3 Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-3 Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-3 Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-3 Arena'!$D$8),ABS('F6-3 Arena'!$D$8-Key!$C$72)&lt;=1E-9*MAX(1,ABS(Key!$C$72))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NETWORKDAYS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F6-3 Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use NETWORKDAYS")))))</f>
@@ -8187,10 +8193,10 @@
         <v>223</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(ISBLANK('F6-3 Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('F6-3 Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F6-3 Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F6-3 Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F6-3 Arena'!$D$9),ABS('F6-3 Arena'!$D$9-Key!$C$73)&lt;=1E-9*MAX(1,ABS(Key!$C$73))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"WORKDAY"&amp;"(",UPPER(_xlfn.FORMULATEXT('F6-3 Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use WORKDAY")))))</f>
@@ -8338,7 +8344,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8351,10 +8357,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8373,7 +8379,7 @@
         <v>46096</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D6" s="29"/>
     </row>
@@ -8385,19 +8391,19 @@
         <v>46143</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D7" s="29"/>
     </row>
     <row r="8" spans="1:4">
       <c r="C8" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D8" s="30"/>
     </row>
     <row r="9" spans="1:4">
       <c r="C9" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D9" s="29"/>
     </row>
@@ -8429,7 +8435,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8440,7 +8446,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8459,7 +8465,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -8470,19 +8476,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C8" s="32" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -8491,7 +8497,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C9" s="32">
         <v>12</v>
@@ -8499,7 +8505,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F6-1 Calendar'!$G$17:$G$53)&gt;=300*0.5,SUM('F6-2 Date Math'!$G$13:$G$39)&gt;=200*0.5,SUM('F6-3 Deadlines'!$G$14:$G$42)&gt;=220*0.5),"OPEN","LOCKED")</f>
@@ -8512,7 +8518,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -8546,7 +8552,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B14" s="33" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function moves a date forward or back by whole months?  (from F6-3 Deadlines)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8569,7 +8575,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B15" s="33" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which function returns the last day of a month?  (from F6-3 Deadlines)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8592,7 +8598,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B16" s="33" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which function counts the working days between two dates?  (from F6-3 Deadlines)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8615,7 +8621,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B17" s="33" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which function returns the date a number of working days later?  (from F6-3 Deadlines)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8638,7 +8644,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B18" s="33" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which XLOOKUP argument number sets the result when no match is found?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8661,7 +8667,7 @@
     </row>
     <row r="19" spans="1:7" ht="51.25" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B19" s="33" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","If the return array is E6:F20, how many columns does the result spill into?  (from F4-2 Safety Net)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8684,7 +8690,7 @@
     </row>
     <row r="20" spans="1:7" ht="51.25" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B20" s="33" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which classic function searches the first column of a table and returns a column by number?  (from F4-3 Old School)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8707,7 +8713,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B21" s="33" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which 4th argument makes VLOOKUP find an exact match?  (from F4-3 Old School)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8730,7 +8736,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8741,7 +8747,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8769,14 +8775,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B26" s="33" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In D6 return the year of B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$6),ABS('Boss Arena'!$D$6-Key!$C$82)&lt;=1E-9*MAX(1,ABS(Key!$C$82))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"YEAR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use YEAR"))))),"LOCKED")</f>
@@ -8794,14 +8800,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B27" s="33" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In D7 return the weekday number of B6 (Sunday = 1).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$7),ABS('Boss Arena'!$D$7-Key!$C$83)&lt;=1E-9*MAX(1,ABS(Key!$C$83))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"WEEKDAY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use WEEKDAY"))))),"LOCKED")</f>
@@ -8819,14 +8825,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B28" s="33" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In D8 count the days from B6 to B7.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$8),ABS('Boss Arena'!$D$8-Key!$C$84)&lt;=1E-9*MAX(1,ABS(Key!$C$84))),FALSE))),"✘ TRY AGAIN","✔ CLEAR")))),"LOCKED")</f>
@@ -8844,14 +8850,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B29" s="33" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In D9 count the full years from B8 to B6 with DATEDIF.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$9),ABS('Boss Arena'!$D$9-Key!$C$85)&lt;=1E-9*MAX(1,ABS(Key!$C$85))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"DATEDIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use DATEDIF"))))),"LOCKED")</f>
@@ -8869,14 +8875,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B30" s="33" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In D10 return the date 2 months after B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$10),ABS('Boss Arena'!$D$10-Key!$C$86)&lt;=1E-9*MAX(1,ABS(Key!$C$86))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EDATE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use EDATE"))))),"LOCKED")</f>
@@ -8894,14 +8900,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B31" s="33" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In D11 return the last day of B7's month.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$11),ABS('Boss Arena'!$D$11-Key!$C$87)&lt;=1E-9*MAX(1,ABS(Key!$C$87))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EOMONTH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use EOMONTH"))))),"LOCKED")</f>
@@ -8919,14 +8925,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B32" s="33" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In D12 count the working days from B6 to B7.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$12),ABS('Boss Arena'!$D$12-Key!$C$88)&lt;=1E-9*MAX(1,ABS(Key!$C$88))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NETWORKDAYS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use NETWORKDAYS"))))),"LOCKED")</f>
@@ -8944,14 +8950,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B33" s="33" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In D13 return the date 15 working days after B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$13),ABS('Boss Arena'!$D$13-Key!$C$89)&lt;=1E-9*MAX(1,ABS(Key!$C$89))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"WORKDAY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$13)))))),"✔ CLEAR","✘ CLOSE · right value, but use WORKDAY"))))),"LOCKED")</f>
@@ -9069,7 +9075,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9082,10 +9088,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -9122,43 +9128,43 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B8" s="28">
         <v>43585</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D8" s="30"/>
     </row>
     <row r="9" spans="1:4">
       <c r="C9" s="5" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D9" s="30"/>
     </row>
     <row r="10" spans="1:4">
       <c r="C10" s="5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D10" s="29"/>
     </row>
     <row r="11" spans="1:4">
       <c r="C11" s="5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D11" s="29"/>
     </row>
     <row r="12" spans="1:4">
       <c r="C12" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D12" s="30"/>
     </row>
     <row r="13" spans="1:4">
       <c r="C13" s="5" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D13" s="29"/>
     </row>

--- a/workbooks/10 Formulas 6 - Dates.xlsx
+++ b/workbooks/10 Formulas 6 - Dates.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="642">
   <si>
     <t>Challenge</t>
   </si>
@@ -2105,9 +2105,24 @@
     <t>0</t>
   </si>
   <si>
+    <t>=FALSE</t>
+  </si>
+  <si>
+    <t>=FALSE(</t>
+  </si>
+  <si>
+    <t>=FALSE()</t>
+  </si>
+  <si>
     <t>FALSE</t>
   </si>
   <si>
+    <t>FALSE(</t>
+  </si>
+  <si>
+    <t>FALSE()</t>
+  </si>
+  <si>
     <t>F8</t>
   </si>
   <si>
@@ -2315,7 +2330,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ DATES</t>
@@ -3105,7 +3120,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3115,12 +3130,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3130,32 +3145,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3165,30 +3180,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F6-1 Calendar'!$G$17:$G$53)&amp;" / 300"</f>
@@ -3203,15 +3218,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F6-2 Date Math'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3226,15 +3241,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F6-3 Deadlines'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3249,15 +3264,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3272,12 +3287,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B18" s="12" cm="1" t="str">
         <f t="array" ref="B18">(SUM('F6-1 Calendar'!$G$17:$G$53)+SUM('F6-2 Date Math'!$G$13:$G$39)+SUM('F6-3 Deadlines'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 880"</f>
@@ -3286,19 +3301,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('F6-1 Calendar'!$G$17:$G$53)+SUM('F6-2 Date Math'!$G$13:$G$39)+SUM('F6-3 Deadlines'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/880,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=12),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 12)","—")</f>
@@ -3307,16 +3322,16 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
-        <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Start!$E$16="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>F6-1 Calendar</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3364,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3357,217 +3372,217 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>268</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>157</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>361</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>156</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -4273,7 +4288,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>272</v>
       </c>
@@ -4299,7 +4314,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>274</v>
       </c>
@@ -4325,7 +4340,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>276</v>
       </c>
@@ -4351,7 +4366,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>278</v>
       </c>
@@ -4377,7 +4392,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>280</v>
       </c>
@@ -4403,7 +4418,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>282</v>
       </c>
@@ -4429,7 +4444,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>284</v>
       </c>
@@ -4455,7 +4470,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>293</v>
       </c>
@@ -4481,7 +4496,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>302</v>
       </c>
@@ -4489,10 +4504,43 @@
         <v>303</v>
       </c>
       <c r="E41" t="s">
+        <v>286</v>
+      </c>
+      <c r="F41" t="s">
+        <v>287</v>
+      </c>
+      <c r="G41" t="s">
+        <v>288</v>
+      </c>
+      <c r="H41" t="s">
+        <v>295</v>
+      </c>
+      <c r="I41" t="s">
+        <v>296</v>
+      </c>
+      <c r="J41" t="s">
+        <v>297</v>
+      </c>
+      <c r="K41" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="L41" t="s">
+        <v>290</v>
+      </c>
+      <c r="M41" t="s">
+        <v>291</v>
+      </c>
+      <c r="N41" t="s">
+        <v>298</v>
+      </c>
+      <c r="O41" t="s">
+        <v>299</v>
+      </c>
+      <c r="P41" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>305</v>
       </c>
@@ -4515,7 +4563,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>310</v>
       </c>
@@ -4538,7 +4586,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>314</v>
       </c>
@@ -4561,7 +4609,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>318</v>
       </c>
@@ -4575,7 +4623,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>322</v>
       </c>
@@ -4595,7 +4643,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>328</v>
       </c>
@@ -4621,7 +4669,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>334</v>
       </c>
@@ -5325,7 +5373,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>531</v>
       </c>
@@ -5338,97 +5386,112 @@
       <c r="F81" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81" t="s">
+        <v>535</v>
+      </c>
+      <c r="H81" t="s">
+        <v>536</v>
+      </c>
+      <c r="I81" t="s">
+        <v>537</v>
+      </c>
+      <c r="J81" t="s">
+        <v>538</v>
+      </c>
+      <c r="K81" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C82" cm="1">
         <f t="array" ref="C82">YEAR('Boss Arena'!$B$6)</f>
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B83" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C83" cm="1">
         <f t="array" ref="C83">WEEKDAY('Boss Arena'!$B$6)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B84" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C84" cm="1">
         <f t="array" ref="C84">'Boss Arena'!$B$7-'Boss Arena'!$B$6</f>
         <v>79</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B85" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C85" cm="1">
         <f t="array" ref="C85">DATEDIF('Boss Arena'!$B$8,'Boss Arena'!$B$6,"Y")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B86" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C86" cm="1">
         <f t="array" ref="C86">EDATE('Boss Arena'!$B$6,2)</f>
         <v>46335</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B87" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C87" cm="1">
         <f t="array" ref="C87">EOMONTH('Boss Arena'!$B$7,0)</f>
         <v>46356</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C88" cm="1">
         <f t="array" ref="C88">NETWORKDAYS('Boss Arena'!$B$6,'Boss Arena'!$B$7)</f>
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B89" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C89" cm="1">
         <f t="array" ref="C89">WORKDAY('Boss Arena'!$B$6,15)</f>
@@ -6970,7 +7033,7 @@
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
-        <f t="array" ref="D22">IFERROR(_xlfn.LET(_xlpm.a,'F6-2 Date Math'!$C$22,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$41:$E$41),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D22">IFERROR(_xlfn.LET(_xlpm.a,'F6-2 Date Math'!$C$22,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$41:$P$41),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E22" s="22"/>
@@ -8435,7 +8498,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8446,7 +8509,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8713,7 +8776,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B21" s="33" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which 4th argument makes VLOOKUP find an exact match?  (from F4-3 Old School)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8721,7 +8784,7 @@
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
-        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$F$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$K$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E21" s="22"/>
@@ -8736,7 +8799,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8747,7 +8810,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8775,14 +8838,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B26" s="33" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In D6 return the year of B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$6),ABS('Boss Arena'!$D$6-Key!$C$82)&lt;=1E-9*MAX(1,ABS(Key!$C$82))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"YEAR"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use YEAR"))))),"LOCKED")</f>
@@ -8800,14 +8863,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B27" s="33" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In D7 return the weekday number of B6 (Sunday = 1).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$7),ABS('Boss Arena'!$D$7-Key!$C$83)&lt;=1E-9*MAX(1,ABS(Key!$C$83))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"WEEKDAY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use WEEKDAY"))))),"LOCKED")</f>
@@ -8825,14 +8888,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B28" s="33" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In D8 count the days from B6 to B7.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$8),ABS('Boss Arena'!$D$8-Key!$C$84)&lt;=1E-9*MAX(1,ABS(Key!$C$84))),FALSE))),"✘ TRY AGAIN","✔ CLEAR")))),"LOCKED")</f>
@@ -8850,14 +8913,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B29" s="33" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In D9 count the full years from B8 to B6 with DATEDIF.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$9),ABS('Boss Arena'!$D$9-Key!$C$85)&lt;=1E-9*MAX(1,ABS(Key!$C$85))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"DATEDIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use DATEDIF"))))),"LOCKED")</f>
@@ -8875,17 +8938,17 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B30" s="33" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In D10 return the date 2 months after B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
-        <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$10),ABS('Boss Arena'!$D$10-Key!$C$86)&lt;=1E-9*MAX(1,ABS(Key!$C$86))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EDATE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use EDATE"))))),"LOCKED")</f>
+        <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$10),ABS('Boss Arena'!$D$10-Key!$C$86)&lt;=1E-9*MAX(1,ABS(Key!$C$86))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EDATE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$10))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"DATE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$10))))))),"✔ CLEAR","✘ CLOSE · right value, but use EDATE/DATE"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E30" s="22"/>
@@ -8900,17 +8963,17 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B31" s="33" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In D11 return the last day of B7's month.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
-        <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$11),ABS('Boss Arena'!$D$11-Key!$C$87)&lt;=1E-9*MAX(1,ABS(Key!$C$87))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EOMONTH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use EOMONTH"))))),"LOCKED")</f>
+        <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$11),ABS('Boss Arena'!$D$11-Key!$C$87)&lt;=1E-9*MAX(1,ABS(Key!$C$87))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"EOMONTH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$11))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"DATE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$11))))))),"✔ CLEAR","✘ CLOSE · right value, but use EOMONTH/DATE"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E31" s="22"/>
@@ -8925,14 +8988,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B32" s="33" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In D12 count the working days from B6 to B7.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$12),ABS('Boss Arena'!$D$12-Key!$C$88)&lt;=1E-9*MAX(1,ABS(Key!$C$88))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"NETWORKDAYS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use NETWORKDAYS"))))),"LOCKED")</f>
@@ -8950,14 +9013,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B33" s="33" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In D13 return the date 15 working days after B6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$13),ABS('Boss Arena'!$D$13-Key!$C$89)&lt;=1E-9*MAX(1,ABS(Key!$C$89))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"WORKDAY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$13)))))),"✔ CLEAR","✘ CLOSE · right value, but use WORKDAY"))))),"LOCKED")</f>
